--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/COMBUSTIVEL - 20_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/COMBUSTIVEL - 20_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -449,7 +444,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOMBA COMBUSTIVEL IRON GG160 182293</t>
+          <t>BOMBA COMBUSTIVEL IRON GG160 2016 A 2023 182293</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +452,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,7 +492,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -520,7 +512,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -541,7 +532,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -562,7 +552,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -575,7 +564,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOMBA COMBUSTIVEL IRON FAZER250 027478</t>
+          <t>BOMBA COMBUSTIVEL IRON FAZER250 2018 A 2023 027478</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -583,7 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -601,10 +589,9 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -612,12 +599,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7898616000018</t>
+          <t>7898635123163</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOIA TANQUE BHD SUSUKI YES125 2006 A 2008</t>
+          <t>BOMBA COMBUSTIVEL CAWU XRE300 2013 A 2020</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -625,7 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -633,12 +619,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7899761405482</t>
+          <t>7908073709130</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOIA TANQUE MAGNETRON FAN CG125</t>
+          <t>BOMBA COMBUSTIVEL SMARTFOX BIZ125 2009 A 2010</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -646,7 +632,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -654,12 +639,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7898508618543</t>
+          <t>7895099120356</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BOIA TANQUE FLEX MAGNETRON CG FAN TITAN150 2010 EM DIANTE</t>
+          <t>BOMBA COMBUSTIVEL FLEX IRON XRE300 2012 A 2013</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -667,7 +652,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -675,22 +659,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7898635123163</t>
+          <t>7908073709093</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOMBA COMBUSTIVEL CAWU XRE300 2013 A 2020</t>
+          <t>BOMBA COMBUSTIVEL SMARTFOX POP110I 2015 2018</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>460</t>
         </is>
       </c>
     </row>
@@ -700,12 +679,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7908073709130</t>
+          <t>0751320980885</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BOMBA COMBUSTIVEL SMARTFOX BIZ125 2009 A 2010</t>
+          <t>BOMBA COMBUSTIVEL FLEX IRON FAN TITAN CG150 2001 A 2013 23649</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -713,204 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>0618341649910</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BOIA TANQUE IRON XRE300 2012 189084</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>7908253800817</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BOIA TANQUE TMAC CB300R 2009 A 2012</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>0602883769052</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BOIA TANQUE IRON CB300 2012 189073</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>7908073720548</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BOIA TANQUE SMARTFOX BROS NXR150 2009 A 2010</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>7895099120356</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>BOMBA COMBUSTIVEL FLEX IRON XRE300 2012 A 2013</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>7908073709093</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BOMBA COMBUSTIVEL SMARTFOX POP110I 2015 2018</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>0751320980885</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>BOMBA COMBUSTIVEL FLEX IRON FAN TITAN CG150 2001 A 2013 23649</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>6941655633806</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BOIA TANQUE ALLEN SUSUKI YES125 72336</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>751320976369</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>BOIA TANQUE IRON JET125 WUYANG 122459</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
